--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="74">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -67,6 +70,42 @@
     <t>2026-05-12</t>
   </si>
   <si>
+    <t>2026-05-16</t>
+  </si>
+  <si>
+    <t>2026-05-19</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>1120 Пловдив Радиново</t>
+  </si>
+  <si>
+    <t>1152 Бургас езеро</t>
+  </si>
+  <si>
+    <t>1902 София, О5 Малинова Долина</t>
+  </si>
+  <si>
+    <t>1157 Пловдив Тракия</t>
+  </si>
+  <si>
+    <t>1184 София Дружба2</t>
+  </si>
+  <si>
+    <t>1195 243 Тракия Езеро</t>
+  </si>
+  <si>
+    <t>1925 HW Trakia, 243 km. Sofia direc</t>
+  </si>
+  <si>
+    <t>1192 София, Младост Ал. Малинов</t>
+  </si>
+  <si>
     <t>СВ0202КЕ</t>
   </si>
   <si>
@@ -91,25 +130,94 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>20:08</t>
-  </si>
-  <si>
-    <t>18:04</t>
-  </si>
-  <si>
-    <t>08:41</t>
-  </si>
-  <si>
-    <t>23:07</t>
-  </si>
-  <si>
-    <t>21:02</t>
-  </si>
-  <si>
-    <t>14:14</t>
-  </si>
-  <si>
-    <t>12:32</t>
+    <t>BLIST.2825 5W 12V W2,1X9,5D BLIX2</t>
+  </si>
+  <si>
+    <t>DIESEL DOUBLE FILTERED</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>20:08:00</t>
+  </si>
+  <si>
+    <t>18:04:00</t>
+  </si>
+  <si>
+    <t>08:41:00</t>
+  </si>
+  <si>
+    <t>23:07:00</t>
+  </si>
+  <si>
+    <t>20:59:00</t>
+  </si>
+  <si>
+    <t>14:14:00</t>
+  </si>
+  <si>
+    <t>12:33:00</t>
+  </si>
+  <si>
+    <t>15:15:00</t>
+  </si>
+  <si>
+    <t>11:45:00</t>
+  </si>
+  <si>
+    <t>14:37:00</t>
+  </si>
+  <si>
+    <t>17:42:00</t>
+  </si>
+  <si>
+    <t>09:48:00</t>
+  </si>
+  <si>
+    <t>13:44:00</t>
+  </si>
+  <si>
+    <t>3231555195 3231555195</t>
+  </si>
+  <si>
+    <t>3231553714 3231553714</t>
+  </si>
+  <si>
+    <t>3231529097 3231529097</t>
+  </si>
+  <si>
+    <t>3231604399 3231604399</t>
+  </si>
+  <si>
+    <t>3231607523 3231607523</t>
+  </si>
+  <si>
+    <t>3231682902 3231682902</t>
+  </si>
+  <si>
+    <t>3231768406 3231768406</t>
+  </si>
+  <si>
+    <t>3231978403 3231978403</t>
+  </si>
+  <si>
+    <t>3231973164 3231973164</t>
+  </si>
+  <si>
+    <t>3231972662 3231972662</t>
+  </si>
+  <si>
+    <t>3232103427 3232103427</t>
+  </si>
+  <si>
+    <t>3232150036 3232150036</t>
+  </si>
+  <si>
+    <t>3232421715 3232421715</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2</t>
@@ -533,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -542,16 +650,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -591,385 +700,757 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1120</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F2">
         <v>23.35</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2">
         <v>1.43</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>33.39</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.54</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>35.96</v>
       </c>
-      <c r="K2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="M2">
-        <v>188101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3">
-        <v>1152</v>
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F3">
         <v>15.68</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3">
         <v>1.43</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>22.42</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.53</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>23.99</v>
       </c>
-      <c r="K3" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3">
+      <c r="L3" t="s">
+        <v>43</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="M3">
-        <v>192170</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="N3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4">
-        <v>1902</v>
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F4">
         <v>53.39</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4">
         <v>1.66</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>88.63</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.8</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>96.09999999999999</v>
       </c>
-      <c r="K4" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4">
+      <c r="L4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="M4">
-        <v>80537</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="N4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5">
-        <v>1152</v>
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F5">
         <v>23.83</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5">
         <v>1.46</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>34.79</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.53</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>36.46</v>
       </c>
-      <c r="K5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L5">
+      <c r="L5" t="s">
+        <v>45</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="M5">
-        <v>192689</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6">
-        <v>1157</v>
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F6">
         <v>21.26</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6">
         <v>1.46</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>31.04</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.54</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>32.74</v>
       </c>
-      <c r="K6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L6">
+      <c r="L6" t="s">
+        <v>46</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="M6">
-        <v>230437</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="N6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7">
-        <v>1120</v>
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F7">
         <v>27.83</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7">
         <v>1.46</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>40.63</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.55</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>43.14</v>
       </c>
-      <c r="K7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L7">
+      <c r="L7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M7">
         <v>0</v>
       </c>
-      <c r="M7">
-        <v>74162</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="N7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8">
-        <v>1184</v>
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F8">
         <v>33.52</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8">
         <v>1.65</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>55.31</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.79</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>60</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
+        <v>48</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
         <v>31</v>
       </c>
-      <c r="L8">
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9">
+        <v>45.34</v>
+      </c>
+      <c r="G9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9">
+        <v>1.64</v>
+      </c>
+      <c r="I9" s="1">
+        <v>74.36</v>
+      </c>
+      <c r="J9">
+        <v>1.76</v>
+      </c>
+      <c r="K9" s="1">
+        <v>79.8</v>
+      </c>
+      <c r="L9" t="s">
+        <v>49</v>
+      </c>
+      <c r="M9">
         <v>0</v>
       </c>
-      <c r="M8">
-        <v>497860</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="3" t="s">
+      <c r="N9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="4" t="s">
+      <c r="D10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10">
+        <v>24.76</v>
+      </c>
+      <c r="G10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10">
+        <v>1.64</v>
+      </c>
+      <c r="I10" s="1">
+        <v>40.61</v>
+      </c>
+      <c r="J10">
+        <v>1.78</v>
+      </c>
+      <c r="K10" s="1">
+        <v>44.07</v>
+      </c>
+      <c r="L10" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11">
+        <v>27.81</v>
+      </c>
+      <c r="G11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11">
+        <v>1.64</v>
+      </c>
+      <c r="I11" s="1">
+        <v>45.61</v>
+      </c>
+      <c r="J11">
+        <v>1.78</v>
+      </c>
+      <c r="K11" s="1">
+        <v>49.5</v>
+      </c>
+      <c r="L11" t="s">
+        <v>51</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="4" t="s">
+      <c r="E12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12">
+        <v>27.76</v>
+      </c>
+      <c r="G12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12">
+        <v>1.49</v>
+      </c>
+      <c r="I12" s="1">
+        <v>41.36</v>
+      </c>
+      <c r="J12">
+        <v>1.54</v>
+      </c>
+      <c r="K12" s="1">
+        <v>42.75</v>
+      </c>
+      <c r="L12" t="s">
+        <v>52</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13">
+        <v>29.14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13">
+        <v>1.63</v>
+      </c>
+      <c r="I13" s="1">
+        <v>47.5</v>
+      </c>
+      <c r="J13">
+        <v>1.75</v>
+      </c>
+      <c r="K13" s="1">
+        <v>51</v>
+      </c>
+      <c r="L13" t="s">
+        <v>53</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" t="s">
+        <v>41</v>
+      </c>
+      <c r="H14">
+        <v>1.69</v>
+      </c>
+      <c r="I14" s="1">
+        <v>1.69</v>
+      </c>
+      <c r="J14">
+        <v>1.69</v>
+      </c>
+      <c r="K14" s="1">
+        <v>1.69</v>
+      </c>
+      <c r="L14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15">
+        <v>57.07</v>
+      </c>
+      <c r="G15" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15">
+        <v>1.87</v>
+      </c>
+      <c r="I15" s="1">
+        <v>106.72</v>
+      </c>
+      <c r="J15">
+        <v>1.99</v>
+      </c>
+      <c r="K15" s="1">
+        <v>113.57</v>
+      </c>
+      <c r="L15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="6">
+        <v>213.96</v>
+      </c>
+      <c r="C20" s="6">
+        <v>6</v>
+      </c>
+      <c r="D20" s="7">
+        <v>1.6453</v>
+      </c>
+      <c r="E20" s="6">
+        <v>352.02</v>
+      </c>
+      <c r="F20" s="6">
+        <v>380.47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="6">
-        <v>111.95</v>
-      </c>
-      <c r="C13" s="6">
-        <v>5</v>
-      </c>
-      <c r="D13" s="7">
-        <v>1.4495</v>
-      </c>
-      <c r="E13" s="6">
-        <v>162.27</v>
-      </c>
-      <c r="F13" s="6">
-        <v>172.29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="6">
-        <v>86.91</v>
-      </c>
-      <c r="C14" s="6">
-        <v>2</v>
-      </c>
-      <c r="D14" s="7">
-        <v>1.6562</v>
-      </c>
-      <c r="E14" s="6">
-        <v>143.94</v>
-      </c>
-      <c r="F14" s="6">
-        <v>156.1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="9">
-        <v>198.86</v>
-      </c>
-      <c r="C15" s="9">
-        <v>7</v>
-      </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="9">
-        <v>306.21</v>
-      </c>
-      <c r="F15" s="9">
-        <v>328.39</v>
+      <c r="B21" s="6">
+        <v>139.71</v>
+      </c>
+      <c r="C21" s="6">
+        <v>6</v>
+      </c>
+      <c r="D21" s="7">
+        <v>1.4575</v>
+      </c>
+      <c r="E21" s="6">
+        <v>203.63</v>
+      </c>
+      <c r="F21" s="6">
+        <v>215.04</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="6">
+        <v>57.07</v>
+      </c>
+      <c r="C22" s="6">
+        <v>1</v>
+      </c>
+      <c r="D22" s="7">
+        <v>1.87</v>
+      </c>
+      <c r="E22" s="6">
+        <v>106.72</v>
+      </c>
+      <c r="F22" s="6">
+        <v>113.57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="6">
+        <v>1</v>
+      </c>
+      <c r="C23" s="6">
+        <v>1</v>
+      </c>
+      <c r="D23" s="7">
+        <v>1.69</v>
+      </c>
+      <c r="E23" s="6">
+        <v>1.69</v>
+      </c>
+      <c r="F23" s="6">
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="9">
+        <v>411.74</v>
+      </c>
+      <c r="C24" s="9">
+        <v>14</v>
+      </c>
+      <c r="D24" s="7"/>
+      <c r="E24" s="9">
+        <v>664.0599999999999</v>
+      </c>
+      <c r="F24" s="9">
+        <v>710.77</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2.xlsx
@@ -271,7 +271,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -281,12 +281,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -336,17 +330,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="49">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-03</t>
   </si>
   <si>
@@ -64,16 +73,16 @@
     <t>2026-06-19</t>
   </si>
   <si>
-    <t>София Малинова Долина</t>
-  </si>
-  <si>
-    <t>София Малинов</t>
-  </si>
-  <si>
-    <t>София Дружба 2</t>
-  </si>
-  <si>
-    <t>София Младост</t>
+    <t>1902 София, О5 Малинова Долина</t>
+  </si>
+  <si>
+    <t>1192 София, Младост Ал. Малинов</t>
+  </si>
+  <si>
+    <t>1184 София Дружба2</t>
+  </si>
+  <si>
+    <t>1901 София, Младост 4-ти км</t>
   </si>
   <si>
     <t>СВ6789ХА</t>
@@ -100,22 +109,40 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-06-03 09:10:10</t>
-  </si>
-  <si>
-    <t>2026-06-05 18:59:21</t>
-  </si>
-  <si>
-    <t>2026-06-16 09:10:27</t>
-  </si>
-  <si>
-    <t>2026-06-17 17:13:07</t>
-  </si>
-  <si>
-    <t>2026-06-19 15:43:43</t>
-  </si>
-  <si>
-    <t>2026-06-19 18:42:22</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>09:10:00</t>
+  </si>
+  <si>
+    <t>18:59:00</t>
+  </si>
+  <si>
+    <t>17:13:00</t>
+  </si>
+  <si>
+    <t>15:41:00</t>
+  </si>
+  <si>
+    <t>18:42:00</t>
+  </si>
+  <si>
+    <t>3232796484 3232796484</t>
+  </si>
+  <si>
+    <t>3232913211 3232913211</t>
+  </si>
+  <si>
+    <t>3233433921 3233433921</t>
+  </si>
+  <si>
+    <t>3233490347 3233490347</t>
+  </si>
+  <si>
+    <t>3233578282 3233578282</t>
+  </si>
+  <si>
+    <t>3233502880 3233502880</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2</t>
@@ -533,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -542,14 +569,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -583,220 +613,283 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F2">
         <v>59.55</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2">
         <v>1.6</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>95.28</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.71</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>101.83</v>
       </c>
-      <c r="K2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F3">
         <v>28.52</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3">
         <v>1.5</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>42.78</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.56</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>44.49</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>26</v>
       </c>
       <c r="F4">
         <v>46.8</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4">
         <v>1.55</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>72.54000000000001</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.59</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>74.41</v>
       </c>
-      <c r="K4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F5">
         <v>43.15</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5">
         <v>1.54</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>66.45</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.59</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>68.61</v>
       </c>
-      <c r="K5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F6">
         <v>33.14</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6">
         <v>1.54</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>51.04</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.58</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>52.36</v>
       </c>
-      <c r="K6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F7">
         <v>25.81</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7">
         <v>1.45</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>37.42</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.54</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>39.75</v>
       </c>
-      <c r="K7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L7" t="s">
+        <v>36</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -804,29 +897,29 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:14">
       <c r="A11" s="4" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B12" s="6">
         <v>182.64</v>
@@ -844,9 +937,9 @@
         <v>297.21</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:14">
       <c r="A13" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B13" s="6">
         <v>54.33</v>
@@ -864,9 +957,9 @@
         <v>84.23999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:14">
       <c r="A14" s="8" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B14" s="9">
         <v>236.97</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="66">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-02</t>
   </si>
   <si>
@@ -61,31 +67,133 @@
     <t>2026-07-06</t>
   </si>
   <si>
-    <t>Тракия Езеро</t>
-  </si>
-  <si>
-    <t>АМ Тракия</t>
-  </si>
-  <si>
-    <t>София Малинова Долина</t>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-26</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>1195 243 Тракия Езеро</t>
+  </si>
+  <si>
+    <t>1925 HW Trakia, 243 km. Sofia direc</t>
+  </si>
+  <si>
+    <t>1902 София, О5 Малинова Долина</t>
+  </si>
+  <si>
+    <t>1192 София, Младост Ал. Малинов</t>
+  </si>
+  <si>
+    <t>1184 София Дружба2</t>
+  </si>
+  <si>
+    <t>1152 Бургас езеро</t>
+  </si>
+  <si>
+    <t>1157 Пловдив Тракия</t>
+  </si>
+  <si>
+    <t>1133 Кресна Е 79</t>
   </si>
   <si>
     <t>СВ6789ХА</t>
   </si>
   <si>
+    <t>СВ0202КЕ</t>
+  </si>
+  <si>
+    <t>СВ9499ХВ</t>
+  </si>
+  <si>
     <t>78970153027721223</t>
   </si>
   <si>
+    <t>78970153027721249</t>
+  </si>
+  <si>
+    <t>78970153027721231</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-07-02 18:28:00</t>
-  </si>
-  <si>
-    <t>2026-07-04 13:28:15</t>
-  </si>
-  <si>
-    <t>2026-07-06 10:57:14</t>
+    <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>18:26:00</t>
+  </si>
+  <si>
+    <t>13:28:00</t>
+  </si>
+  <si>
+    <t>10:57:00</t>
+  </si>
+  <si>
+    <t>17:06:00</t>
+  </si>
+  <si>
+    <t>09:48:00</t>
+  </si>
+  <si>
+    <t>17:53:00</t>
+  </si>
+  <si>
+    <t>15:29:00</t>
+  </si>
+  <si>
+    <t>17:19:00</t>
+  </si>
+  <si>
+    <t>10:11:00</t>
+  </si>
+  <si>
+    <t>08:35:00</t>
+  </si>
+  <si>
+    <t>3234202865 3234202865</t>
+  </si>
+  <si>
+    <t>3234310740 3234310740</t>
+  </si>
+  <si>
+    <t>3234388766 3234388766</t>
+  </si>
+  <si>
+    <t>3234948420 3234948420</t>
+  </si>
+  <si>
+    <t>3235090558 3235090558</t>
+  </si>
+  <si>
+    <t>3235298940 3235298940</t>
+  </si>
+  <si>
+    <t>3235292075 3235292075</t>
+  </si>
+  <si>
+    <t>3235377929 3235377929</t>
+  </si>
+  <si>
+    <t>3235426640 3235426640</t>
+  </si>
+  <si>
+    <t>3235524919 3235524919</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2</t>
@@ -503,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -512,15 +620,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -557,192 +667,544 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F2">
         <v>26.95</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2">
         <v>1.43</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>38.54</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.55</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>41.77</v>
       </c>
-      <c r="K2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M2">
         <v>50000</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="N2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F3">
         <v>37.57</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3">
         <v>1.44</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>54.1</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.56</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>58.61</v>
       </c>
-      <c r="K3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3">
+      <c r="L3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3">
         <v>50056</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="N3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F4">
         <v>27</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4">
         <v>1.44</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>38.88</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.55</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>41.85</v>
       </c>
-      <c r="K4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L4">
+      <c r="L4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="3" t="s">
+      <c r="N4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5">
+        <v>29.8</v>
+      </c>
+      <c r="G5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5">
+        <v>1.4</v>
+      </c>
+      <c r="I5" s="1">
+        <v>41.72</v>
+      </c>
+      <c r="J5">
+        <v>1.51</v>
+      </c>
+      <c r="K5" s="1">
+        <v>45</v>
+      </c>
+      <c r="L5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6">
+        <v>36.05</v>
+      </c>
+      <c r="G6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6">
+        <v>1.58</v>
+      </c>
+      <c r="I6" s="1">
+        <v>56.96</v>
+      </c>
+      <c r="J6">
+        <v>1.68</v>
+      </c>
+      <c r="K6" s="1">
+        <v>60.56</v>
+      </c>
+      <c r="L6" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7">
+        <v>21.66</v>
+      </c>
+      <c r="G7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7">
+        <v>1.43</v>
+      </c>
+      <c r="I7" s="1">
+        <v>30.97</v>
+      </c>
+      <c r="J7">
+        <v>1.55</v>
+      </c>
+      <c r="K7" s="1">
+        <v>33.57</v>
+      </c>
+      <c r="L7" t="s">
+        <v>45</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8">
+        <v>17.08</v>
+      </c>
+      <c r="G8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8">
+        <v>1.43</v>
+      </c>
+      <c r="I8" s="1">
+        <v>24.42</v>
+      </c>
+      <c r="J8">
+        <v>1.57</v>
+      </c>
+      <c r="K8" s="1">
+        <v>26.82</v>
+      </c>
+      <c r="L8" t="s">
+        <v>46</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="4" t="s">
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9">
+        <v>21.93</v>
+      </c>
+      <c r="G9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9">
+        <v>1.43</v>
+      </c>
+      <c r="I9" s="1">
+        <v>31.36</v>
+      </c>
+      <c r="J9">
+        <v>1.59</v>
+      </c>
+      <c r="K9" s="1">
+        <v>34.87</v>
+      </c>
+      <c r="L9" t="s">
+        <v>47</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="6">
-        <v>91.52</v>
-      </c>
-      <c r="C9" s="6">
-        <v>3</v>
-      </c>
-      <c r="D9" s="7">
-        <v>1.4371</v>
-      </c>
-      <c r="E9" s="6">
-        <v>131.52</v>
-      </c>
-      <c r="F9" s="6">
-        <v>142.23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="9">
-        <v>91.52</v>
-      </c>
-      <c r="C10" s="9">
-        <v>3</v>
-      </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="9">
-        <v>131.52</v>
-      </c>
-      <c r="F10" s="9">
-        <v>142.23</v>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10">
+        <v>44.62</v>
+      </c>
+      <c r="G10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10">
+        <v>1.65</v>
+      </c>
+      <c r="I10" s="1">
+        <v>73.62</v>
+      </c>
+      <c r="J10">
+        <v>1.76</v>
+      </c>
+      <c r="K10" s="1">
+        <v>78.53</v>
+      </c>
+      <c r="L10" t="s">
+        <v>48</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11">
+        <v>10.46</v>
+      </c>
+      <c r="G11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11">
+        <v>1.7</v>
+      </c>
+      <c r="I11" s="1">
+        <v>17.78</v>
+      </c>
+      <c r="J11">
+        <v>1.78</v>
+      </c>
+      <c r="K11" s="1">
+        <v>18.62</v>
+      </c>
+      <c r="L11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M11">
+        <v>51000</v>
+      </c>
+      <c r="N11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="6">
+        <v>182.65</v>
+      </c>
+      <c r="C16" s="6">
+        <v>6</v>
+      </c>
+      <c r="D16" s="7">
+        <v>1.5323</v>
+      </c>
+      <c r="E16" s="6">
+        <v>279.88</v>
+      </c>
+      <c r="F16" s="6">
+        <v>299.94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="6">
+        <v>90.47</v>
+      </c>
+      <c r="C17" s="6">
+        <v>4</v>
+      </c>
+      <c r="D17" s="7">
+        <v>1.42</v>
+      </c>
+      <c r="E17" s="6">
+        <v>128.47</v>
+      </c>
+      <c r="F17" s="6">
+        <v>140.26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="9">
+        <v>273.12</v>
+      </c>
+      <c r="C18" s="9">
+        <v>10</v>
+      </c>
+      <c r="D18" s="7"/>
+      <c r="E18" s="9">
+        <v>408.35</v>
+      </c>
+      <c r="F18" s="9">
+        <v>440.2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A14:F14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2.xlsx
@@ -220,7 +220,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1155,7 +1155,7 @@
         <v>6</v>
       </c>
       <c r="D16" s="7">
-        <v>1.5323</v>
+        <v>1.53233</v>
       </c>
       <c r="E16" s="6">
         <v>279.88</v>
@@ -1175,7 +1175,7 @@
         <v>4</v>
       </c>
       <c r="D17" s="7">
-        <v>1.42</v>
+        <v>1.420029</v>
       </c>
       <c r="E17" s="6">
         <v>128.47</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="67">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -611,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -624,13 +627,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -673,450 +676,483 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2">
-        <v>26.95</v>
+        <v>26.948</v>
       </c>
       <c r="G2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H2">
-        <v>1.43</v>
+        <v>1.399</v>
       </c>
       <c r="I2" s="1">
-        <v>38.54</v>
+        <v>1.429</v>
       </c>
       <c r="J2">
+        <v>38.508692</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.55</v>
       </c>
-      <c r="K2" s="1">
-        <v>41.77</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="L2" s="1">
+        <v>41.7694</v>
+      </c>
+      <c r="M2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2">
+        <v>50000</v>
+      </c>
+      <c r="O2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3">
+        <v>37.571</v>
+      </c>
+      <c r="G3" t="s">
         <v>40</v>
       </c>
-      <c r="M2">
-        <v>50000</v>
-      </c>
-      <c r="N2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3">
-        <v>37.57</v>
-      </c>
-      <c r="G3" t="s">
-        <v>39</v>
-      </c>
       <c r="H3">
-        <v>1.44</v>
+        <v>1.406</v>
       </c>
       <c r="I3" s="1">
-        <v>54.1</v>
+        <v>1.436</v>
       </c>
       <c r="J3">
+        <v>53.951956</v>
+      </c>
+      <c r="K3" s="1">
         <v>1.56</v>
       </c>
-      <c r="K3" s="1">
-        <v>58.61</v>
-      </c>
-      <c r="L3" t="s">
-        <v>41</v>
-      </c>
-      <c r="M3">
+      <c r="L3" s="1">
+        <v>58.61076</v>
+      </c>
+      <c r="M3" t="s">
+        <v>42</v>
+      </c>
+      <c r="N3">
         <v>50056</v>
       </c>
-      <c r="N3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F4">
         <v>27</v>
       </c>
       <c r="G4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4">
+        <v>1.406</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.436</v>
+      </c>
+      <c r="J4">
+        <v>38.772</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="L4" s="1">
+        <v>41.85</v>
+      </c>
+      <c r="M4" t="s">
+        <v>43</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
         <v>39</v>
       </c>
-      <c r="H4">
-        <v>1.44</v>
-      </c>
-      <c r="I4" s="1">
-        <v>38.88</v>
-      </c>
-      <c r="J4">
+      <c r="F5">
+        <v>29.801</v>
+      </c>
+      <c r="G5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5">
+        <v>1.369</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.399</v>
+      </c>
+      <c r="J5">
+        <v>41.691599</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="L5" s="1">
+        <v>44.99951</v>
+      </c>
+      <c r="M5" t="s">
+        <v>44</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6">
+        <v>36.048</v>
+      </c>
+      <c r="G6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6">
+        <v>1.546</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.576</v>
+      </c>
+      <c r="J6">
+        <v>56.811648</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="L6" s="1">
+        <v>60.56064</v>
+      </c>
+      <c r="M6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7">
+        <v>21.658</v>
+      </c>
+      <c r="G7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7">
+        <v>1.401</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.431</v>
+      </c>
+      <c r="J7">
+        <v>30.992598</v>
+      </c>
+      <c r="K7" s="1">
         <v>1.55</v>
       </c>
-      <c r="K4" s="1">
-        <v>41.85</v>
-      </c>
-      <c r="L4" t="s">
-        <v>42</v>
-      </c>
-      <c r="M4">
+      <c r="L7" s="1">
+        <v>33.5699</v>
+      </c>
+      <c r="M7" t="s">
+        <v>46</v>
+      </c>
+      <c r="N7">
         <v>0</v>
       </c>
-      <c r="N4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="O7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8">
+        <v>17.083</v>
+      </c>
+      <c r="G8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8">
+        <v>1.401</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1.431</v>
+      </c>
+      <c r="J8">
+        <v>24.445773</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="L8" s="1">
+        <v>26.82031</v>
+      </c>
+      <c r="M8" t="s">
+        <v>47</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9">
+        <v>21.931</v>
+      </c>
+      <c r="G9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9">
+        <v>1.401</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1.431</v>
+      </c>
+      <c r="J9">
+        <v>31.383261</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1.59</v>
+      </c>
+      <c r="L9" s="1">
+        <v>34.87029</v>
+      </c>
+      <c r="M9" t="s">
+        <v>48</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
         <v>26</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C10" t="s">
         <v>32</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D10" t="s">
         <v>35</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E10" t="s">
         <v>38</v>
       </c>
-      <c r="F5">
-        <v>29.8</v>
-      </c>
-      <c r="G5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5">
-        <v>1.4</v>
-      </c>
-      <c r="I5" s="1">
-        <v>41.72</v>
-      </c>
-      <c r="J5">
-        <v>1.51</v>
-      </c>
-      <c r="K5" s="1">
-        <v>45</v>
-      </c>
-      <c r="L5" t="s">
-        <v>43</v>
-      </c>
-      <c r="M5">
+      <c r="F10">
+        <v>44.619</v>
+      </c>
+      <c r="G10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10">
+        <v>1.619</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1.649</v>
+      </c>
+      <c r="J10">
+        <v>73.576731</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1.76</v>
+      </c>
+      <c r="L10" s="1">
+        <v>78.52943999999999</v>
+      </c>
+      <c r="M10" t="s">
+        <v>49</v>
+      </c>
+      <c r="N10">
         <v>0</v>
       </c>
-      <c r="N5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6">
-        <v>36.05</v>
-      </c>
-      <c r="G6" t="s">
-        <v>39</v>
-      </c>
-      <c r="H6">
-        <v>1.58</v>
-      </c>
-      <c r="I6" s="1">
-        <v>56.96</v>
-      </c>
-      <c r="J6">
-        <v>1.68</v>
-      </c>
-      <c r="K6" s="1">
-        <v>60.56</v>
-      </c>
-      <c r="L6" t="s">
-        <v>44</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="O10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
         <v>32</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D11" t="s">
         <v>35</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E11" t="s">
         <v>38</v>
       </c>
-      <c r="F7">
-        <v>21.66</v>
-      </c>
-      <c r="G7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7">
-        <v>1.43</v>
-      </c>
-      <c r="I7" s="1">
-        <v>30.97</v>
-      </c>
-      <c r="J7">
-        <v>1.55</v>
-      </c>
-      <c r="K7" s="1">
-        <v>33.57</v>
-      </c>
-      <c r="L7" t="s">
-        <v>45</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8">
-        <v>17.08</v>
-      </c>
-      <c r="G8" t="s">
-        <v>39</v>
-      </c>
-      <c r="H8">
-        <v>1.43</v>
-      </c>
-      <c r="I8" s="1">
-        <v>24.42</v>
-      </c>
-      <c r="J8">
-        <v>1.57</v>
-      </c>
-      <c r="K8" s="1">
-        <v>26.82</v>
-      </c>
-      <c r="L8" t="s">
-        <v>46</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9">
-        <v>21.93</v>
-      </c>
-      <c r="G9" t="s">
-        <v>39</v>
-      </c>
-      <c r="H9">
-        <v>1.43</v>
-      </c>
-      <c r="I9" s="1">
-        <v>31.36</v>
-      </c>
-      <c r="J9">
-        <v>1.59</v>
-      </c>
-      <c r="K9" s="1">
-        <v>34.87</v>
-      </c>
-      <c r="L9" t="s">
-        <v>47</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10">
-        <v>44.62</v>
-      </c>
-      <c r="G10" t="s">
-        <v>39</v>
-      </c>
-      <c r="H10">
-        <v>1.65</v>
-      </c>
-      <c r="I10" s="1">
-        <v>73.62</v>
-      </c>
-      <c r="J10">
-        <v>1.76</v>
-      </c>
-      <c r="K10" s="1">
-        <v>78.53</v>
-      </c>
-      <c r="L10" t="s">
-        <v>48</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" t="s">
-        <v>37</v>
-      </c>
       <c r="F11">
-        <v>10.46</v>
+        <v>10.461</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H11">
-        <v>1.7</v>
+        <v>1.674</v>
       </c>
       <c r="I11" s="1">
-        <v>17.78</v>
+        <v>1.704</v>
       </c>
       <c r="J11">
+        <v>17.825544</v>
+      </c>
+      <c r="K11" s="1">
         <v>1.78</v>
       </c>
-      <c r="K11" s="1">
-        <v>18.62</v>
-      </c>
-      <c r="L11" t="s">
-        <v>49</v>
-      </c>
-      <c r="M11">
+      <c r="L11" s="1">
+        <v>18.62058</v>
+      </c>
+      <c r="M11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N11">
         <v>51000</v>
       </c>
-      <c r="N11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -1124,41 +1160,41 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:15">
       <c r="A15" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="6">
-        <v>182.65</v>
+        <v>182.647</v>
       </c>
       <c r="C16" s="6">
         <v>6</v>
       </c>
       <c r="D16" s="7">
-        <v>1.53233</v>
+        <v>1.529982</v>
       </c>
       <c r="E16" s="6">
-        <v>279.88</v>
+        <v>279.45</v>
       </c>
       <c r="F16" s="6">
         <v>299.94</v>
@@ -1166,19 +1202,19 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B17" s="6">
-        <v>90.47</v>
+        <v>90.473</v>
       </c>
       <c r="C17" s="6">
         <v>4</v>
       </c>
       <c r="D17" s="7">
-        <v>1.420029</v>
+        <v>1.420459</v>
       </c>
       <c r="E17" s="6">
-        <v>128.47</v>
+        <v>128.51</v>
       </c>
       <c r="F17" s="6">
         <v>140.26</v>
@@ -1186,7 +1222,7 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B18" s="9">
         <v>273.12</v>
@@ -1196,7 +1232,7 @@
       </c>
       <c r="D18" s="7"/>
       <c r="E18" s="9">
-        <v>408.35</v>
+        <v>407.96</v>
       </c>
       <c r="F18" s="9">
         <v>440.2</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2/ДЕМАКС ДИ ПИ АЙ АД % ГРУПА 2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="66">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -222,8 +219,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -316,10 +313,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -614,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -627,13 +624,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -676,483 +673,450 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2">
         <v>26.948</v>
       </c>
       <c r="G2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2">
+        <v>1.429</v>
+      </c>
+      <c r="I2" s="1">
+        <v>38.509</v>
+      </c>
+      <c r="J2">
+        <v>1.55</v>
+      </c>
+      <c r="K2" s="1">
+        <v>41.769</v>
+      </c>
+      <c r="L2" t="s">
         <v>40</v>
       </c>
-      <c r="H2">
-        <v>1.399</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.429</v>
-      </c>
-      <c r="J2">
-        <v>38.508692</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L2" s="1">
-        <v>41.7694</v>
-      </c>
-      <c r="M2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>50000</v>
       </c>
-      <c r="O2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3">
         <v>37.571</v>
       </c>
       <c r="G3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H3">
-        <v>1.406</v>
+        <v>1.436</v>
       </c>
       <c r="I3" s="1">
-        <v>1.436</v>
+        <v>53.952</v>
       </c>
       <c r="J3">
-        <v>53.951956</v>
+        <v>1.56</v>
       </c>
       <c r="K3" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L3" s="1">
-        <v>58.61076</v>
-      </c>
-      <c r="M3" t="s">
-        <v>42</v>
-      </c>
-      <c r="N3">
+        <v>58.611</v>
+      </c>
+      <c r="L3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3">
         <v>50056</v>
       </c>
-      <c r="O3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F4">
         <v>27</v>
       </c>
       <c r="G4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H4">
-        <v>1.406</v>
+        <v>1.436</v>
       </c>
       <c r="I4" s="1">
-        <v>1.436</v>
+        <v>38.772</v>
       </c>
       <c r="J4">
-        <v>38.772</v>
+        <v>1.55</v>
       </c>
       <c r="K4" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L4" s="1">
         <v>41.85</v>
       </c>
-      <c r="M4" t="s">
-        <v>43</v>
-      </c>
-      <c r="N4">
+      <c r="L4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="O4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5">
         <v>29.801</v>
       </c>
       <c r="G5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H5">
-        <v>1.369</v>
+        <v>1.399</v>
       </c>
       <c r="I5" s="1">
-        <v>1.399</v>
+        <v>41.692</v>
       </c>
       <c r="J5">
-        <v>41.691599</v>
+        <v>1.51</v>
       </c>
       <c r="K5" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L5" s="1">
-        <v>44.99951</v>
-      </c>
-      <c r="M5" t="s">
-        <v>44</v>
-      </c>
-      <c r="N5">
+        <v>45</v>
+      </c>
+      <c r="L5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="O5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
         <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>38</v>
       </c>
       <c r="F6">
         <v>36.048</v>
       </c>
       <c r="G6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H6">
-        <v>1.546</v>
+        <v>1.576</v>
       </c>
       <c r="I6" s="1">
-        <v>1.576</v>
+        <v>56.812</v>
       </c>
       <c r="J6">
-        <v>56.811648</v>
+        <v>1.68</v>
       </c>
       <c r="K6" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L6" s="1">
-        <v>60.56064</v>
-      </c>
-      <c r="M6" t="s">
-        <v>45</v>
-      </c>
-      <c r="N6">
+        <v>60.561</v>
+      </c>
+      <c r="L6" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="O6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F7">
         <v>21.658</v>
       </c>
       <c r="G7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H7">
-        <v>1.401</v>
+        <v>1.431</v>
       </c>
       <c r="I7" s="1">
-        <v>1.431</v>
+        <v>30.993</v>
       </c>
       <c r="J7">
-        <v>30.992598</v>
+        <v>1.55</v>
       </c>
       <c r="K7" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L7" s="1">
-        <v>33.5699</v>
-      </c>
-      <c r="M7" t="s">
-        <v>46</v>
-      </c>
-      <c r="N7">
+        <v>33.57</v>
+      </c>
+      <c r="L7" t="s">
+        <v>45</v>
+      </c>
+      <c r="M7">
         <v>0</v>
       </c>
-      <c r="O7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F8">
         <v>17.083</v>
       </c>
       <c r="G8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H8">
-        <v>1.401</v>
+        <v>1.431</v>
       </c>
       <c r="I8" s="1">
-        <v>1.431</v>
+        <v>24.446</v>
       </c>
       <c r="J8">
-        <v>24.445773</v>
+        <v>1.57</v>
       </c>
       <c r="K8" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="L8" s="1">
-        <v>26.82031</v>
-      </c>
-      <c r="M8" t="s">
-        <v>47</v>
-      </c>
-      <c r="N8">
+        <v>26.82</v>
+      </c>
+      <c r="L8" t="s">
+        <v>46</v>
+      </c>
+      <c r="M8">
         <v>0</v>
       </c>
-      <c r="O8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="N8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F9">
         <v>21.931</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H9">
-        <v>1.401</v>
+        <v>1.431</v>
       </c>
       <c r="I9" s="1">
-        <v>1.431</v>
+        <v>31.383</v>
       </c>
       <c r="J9">
-        <v>31.383261</v>
+        <v>1.59</v>
       </c>
       <c r="K9" s="1">
-        <v>1.59</v>
-      </c>
-      <c r="L9" s="1">
-        <v>34.87029</v>
-      </c>
-      <c r="M9" t="s">
-        <v>48</v>
-      </c>
-      <c r="N9">
+        <v>34.87</v>
+      </c>
+      <c r="L9" t="s">
+        <v>47</v>
+      </c>
+      <c r="M9">
         <v>0</v>
       </c>
-      <c r="O9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="N9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F10">
         <v>44.619</v>
       </c>
       <c r="G10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H10">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I10" s="1">
-        <v>1.649</v>
+        <v>73.577</v>
       </c>
       <c r="J10">
-        <v>73.576731</v>
+        <v>1.76</v>
       </c>
       <c r="K10" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L10" s="1">
-        <v>78.52943999999999</v>
-      </c>
-      <c r="M10" t="s">
-        <v>49</v>
-      </c>
-      <c r="N10">
+        <v>78.529</v>
+      </c>
+      <c r="L10" t="s">
+        <v>48</v>
+      </c>
+      <c r="M10">
         <v>0</v>
       </c>
-      <c r="O10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="N10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
         <v>31</v>
       </c>
-      <c r="C11" t="s">
-        <v>32</v>
-      </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F11">
         <v>10.461</v>
       </c>
       <c r="G11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H11">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I11" s="1">
-        <v>1.704</v>
+        <v>17.826</v>
       </c>
       <c r="J11">
-        <v>17.825544</v>
+        <v>1.78</v>
       </c>
       <c r="K11" s="1">
-        <v>1.78</v>
-      </c>
-      <c r="L11" s="1">
-        <v>18.62058</v>
-      </c>
-      <c r="M11" t="s">
-        <v>50</v>
-      </c>
-      <c r="N11">
+        <v>18.621</v>
+      </c>
+      <c r="L11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M11">
         <v>51000</v>
       </c>
-      <c r="O11" t="s">
+      <c r="N11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="3" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="A14" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -1160,69 +1124,69 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:14">
       <c r="A15" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="C15" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="D15" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>65</v>
-      </c>
       <c r="E15" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" s="6">
         <v>182.647</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="7">
         <v>6</v>
       </c>
       <c r="D16" s="7">
-        <v>1.529982</v>
-      </c>
-      <c r="E16" s="6">
-        <v>279.45</v>
-      </c>
-      <c r="F16" s="6">
-        <v>299.94</v>
+        <v>1.53</v>
+      </c>
+      <c r="E16" s="7">
+        <v>279.448</v>
+      </c>
+      <c r="F16" s="7">
+        <v>299.941</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B17" s="6">
         <v>90.473</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="7">
         <v>4</v>
       </c>
       <c r="D17" s="7">
-        <v>1.420459</v>
-      </c>
-      <c r="E17" s="6">
-        <v>128.51</v>
-      </c>
-      <c r="F17" s="6">
+        <v>1.42</v>
+      </c>
+      <c r="E17" s="7">
+        <v>128.514</v>
+      </c>
+      <c r="F17" s="7">
         <v>140.26</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B18" s="9">
         <v>273.12</v>
@@ -1232,10 +1196,10 @@
       </c>
       <c r="D18" s="7"/>
       <c r="E18" s="9">
-        <v>407.96</v>
+        <v>407.962</v>
       </c>
       <c r="F18" s="9">
-        <v>440.2</v>
+        <v>440.201</v>
       </c>
     </row>
   </sheetData>
